--- a/corr_matrix/residual_exam3A_3PL.xlsx
+++ b/corr_matrix/residual_exam3A_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>3A01</t>
@@ -525,52 +530,52 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05714885896163142</v>
+        <v>-0.05713190869009823</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02481363697955809</v>
+        <v>0.02483258130696783</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05327522810715765</v>
+        <v>-0.05327320686625123</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1864650850655215</v>
+        <v>-0.1864558704218054</v>
       </c>
       <c r="G2" t="n">
-        <v>0.146585775369217</v>
+        <v>0.1465985542402881</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1229577147621074</v>
+        <v>0.1229631912673144</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1534139358028783</v>
+        <v>0.1534220427572602</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.02185396323078784</v>
+        <v>-0.02185295095155215</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1089188578001027</v>
+        <v>-0.1089239121346346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06042980849747077</v>
+        <v>0.06045481191960975</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07200694831406737</v>
+        <v>-0.07200721574068904</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.06223235290669801</v>
+        <v>-0.06224258984486636</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1392657276480948</v>
+        <v>-0.1392607199602888</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0916503972308273</v>
+        <v>-0.09165673432709796</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2861192760870436</v>
+        <v>0.2861194120485466</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.09085914594505834</v>
+        <v>-0.09085050779983372</v>
       </c>
     </row>
     <row r="3">
@@ -580,55 +585,55 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.05714885896163142</v>
+        <v>-0.05713190869009823</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08876728438304637</v>
+        <v>0.08877421850913039</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1491664340668347</v>
+        <v>0.1491720599195573</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.007810094365840905</v>
+        <v>-0.007806203091613875</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1373053012296276</v>
+        <v>-0.1372953198581802</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2532838286723236</v>
+        <v>-0.2532760263385063</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1165850061042142</v>
+        <v>-0.1165853371239037</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.06654940073437685</v>
+        <v>-0.06654800699118624</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.03291119029085397</v>
+        <v>-0.03290981282705194</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004279317708373074</v>
+        <v>0.004288749201532157</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08360196359806447</v>
+        <v>0.08360710229283419</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.132680053371097</v>
+        <v>-0.1326778922424604</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1107287040595184</v>
+        <v>-0.1107241016210228</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2412834037869715</v>
+        <v>-0.2412801869186034</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3049965723763982</v>
+        <v>-0.3049929745683377</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01425591132601753</v>
+        <v>-0.0142498768740238</v>
       </c>
     </row>
     <row r="4">
@@ -638,55 +643,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02481363697955809</v>
+        <v>0.02483258130696783</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08876728438304637</v>
+        <v>0.08877421850913039</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2312806374635029</v>
+        <v>0.2312808297529335</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09564537884492251</v>
+        <v>-0.0956455485204472</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05598556872681565</v>
+        <v>0.05599479458071485</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2121710404627471</v>
+        <v>-0.2121617015597813</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06153697738428187</v>
+        <v>-0.06153318501219202</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003585578925887138</v>
+        <v>0.003585462311208485</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.004568629074206131</v>
+        <v>-0.004574775415538714</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1353323101048391</v>
+        <v>0.1353406515303948</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08327739985458649</v>
+        <v>-0.083278936877186</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02366213032305863</v>
+        <v>0.02367748914598187</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2928466533276219</v>
+        <v>-0.2928443648818424</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2555073431239664</v>
+        <v>-0.2555084197943746</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2622539373202679</v>
+        <v>-0.2622522932892458</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1440354780577895</v>
+        <v>-0.1440326201203641</v>
       </c>
     </row>
     <row r="5">
@@ -696,55 +701,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.05327522810715765</v>
+        <v>-0.05327320686625123</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1491664340668347</v>
+        <v>0.1491720599195573</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2312806374635029</v>
+        <v>0.2312808297529335</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1750491382403238</v>
+        <v>-0.1750508142062445</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.04859633108170072</v>
+        <v>-0.04859068478145328</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1174574442808879</v>
+        <v>-0.1174582141699974</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3470632353391326</v>
+        <v>-0.3470650437762434</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2551645438026334</v>
+        <v>0.255162225820829</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08454527217265456</v>
+        <v>0.08452891678834798</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03783970617494273</v>
+        <v>0.03784703098808202</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01284317346197137</v>
+        <v>-0.0128546848893997</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1953441468644471</v>
+        <v>-0.1953285942457748</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1935932745111474</v>
+        <v>-0.1935975797300928</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1935707870142529</v>
+        <v>-0.1935833410621786</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.191839201031825</v>
+        <v>-0.1918499048493386</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.05437715338077125</v>
+        <v>-0.05438506220264985</v>
       </c>
     </row>
     <row r="6">
@@ -754,55 +759,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1864650850655215</v>
+        <v>-0.1864558704218054</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.007810094365840905</v>
+        <v>-0.007806203091613875</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09564537884492251</v>
+        <v>-0.0956455485204472</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1750491382403238</v>
+        <v>-0.1750508142062445</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03228682408530704</v>
+        <v>0.03229415399501748</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.05211867914604373</v>
+        <v>-0.05211351874039685</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1737414298673774</v>
+        <v>-0.1737439044889355</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2623123784470487</v>
+        <v>-0.2623152162271145</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05629361931572446</v>
+        <v>-0.05629820108862304</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04911980337398569</v>
+        <v>0.04912443633068477</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1539428266063144</v>
+        <v>-0.1539463953381486</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02690703166057098</v>
+        <v>0.02690847297289807</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.03083024928601621</v>
+        <v>-0.03083520774708307</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2615975856257569</v>
+        <v>-0.2616020899469228</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3386445783876008</v>
+        <v>-0.3386449652654847</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.01876771230800976</v>
+        <v>-0.01877049991952432</v>
       </c>
     </row>
     <row r="7">
@@ -812,55 +817,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.146585775369217</v>
+        <v>0.1465985542402881</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1373053012296276</v>
+        <v>-0.1372953198581802</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05598556872681565</v>
+        <v>0.05599479458071485</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04859633108170072</v>
+        <v>-0.04859068478145328</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03228682408530704</v>
+        <v>0.03229415399501748</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.240187893454789</v>
+        <v>0.2401947788637379</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07060071424123769</v>
+        <v>-0.070603779049991</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2366580315613873</v>
+        <v>-0.2366577275765754</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1781126722146178</v>
+        <v>-0.1781135863358454</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0206189637574075</v>
+        <v>-0.02060065919242438</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09048251672935047</v>
+        <v>-0.09047763086059395</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02564865319920007</v>
+        <v>-0.02565347413816375</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.07476151082895501</v>
+        <v>-0.07475468667727389</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1284688276245625</v>
+        <v>-0.128467717265563</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1024438562367907</v>
+        <v>0.1024476202220046</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1361311127764178</v>
+        <v>-0.1361213172195284</v>
       </c>
     </row>
     <row r="8">
@@ -870,55 +875,55 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1229577147621074</v>
+        <v>0.1229631912673144</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2532838286723236</v>
+        <v>-0.2532760263385063</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2121710404627471</v>
+        <v>-0.2121617015597813</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1174574442808879</v>
+        <v>-0.1174582141699974</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05211867914604373</v>
+        <v>-0.05211351874039685</v>
       </c>
       <c r="G8" t="n">
-        <v>0.240187893454789</v>
+        <v>0.2401947788637379</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1325965717508916</v>
+        <v>0.1325890315918123</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.06677462750004423</v>
+        <v>-0.06678122718484626</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.01397864288864214</v>
+        <v>-0.01398933307941498</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1332992889254884</v>
+        <v>-0.1332799988085527</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1502872731241271</v>
+        <v>-0.1502918345750388</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.03704853513272143</v>
+        <v>-0.03705798757975618</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0393037989885729</v>
+        <v>-0.03930376538405828</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0394168404907396</v>
+        <v>0.03940844743962038</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1225276578364418</v>
+        <v>0.1225239629321348</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02497911170223049</v>
+        <v>0.02498184186088281</v>
       </c>
     </row>
     <row r="9">
@@ -928,55 +933,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1534139358028783</v>
+        <v>0.1534220427572602</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1165850061042142</v>
+        <v>-0.1165853371239037</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06153697738428187</v>
+        <v>-0.06153318501219202</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3470632353391326</v>
+        <v>-0.3470650437762434</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1737414298673774</v>
+        <v>-0.1737439044889355</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.07060071424123769</v>
+        <v>-0.070603779049991</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1325965717508916</v>
+        <v>0.1325890315918123</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.186687509936757</v>
+        <v>0.1866842069862713</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1207979239935361</v>
+        <v>0.1207929392318885</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1470144323185691</v>
+        <v>-0.1470126622324025</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.226061384958911</v>
+        <v>-0.2260650664380562</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01458500950833681</v>
+        <v>-0.01458295775546621</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04841577278798278</v>
+        <v>0.04841205060502528</v>
       </c>
       <c r="P9" t="n">
-        <v>0.07197770583720992</v>
+        <v>0.07197671422373629</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08301605333097707</v>
+        <v>0.08301192870807282</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.1417532282688239</v>
+        <v>-0.1417578894202756</v>
       </c>
     </row>
     <row r="10">
@@ -986,55 +991,55 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.02185396323078784</v>
+        <v>-0.02185295095155215</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.06654940073437685</v>
+        <v>-0.06654800699118624</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003585578925887138</v>
+        <v>0.003585462311208485</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2551645438026334</v>
+        <v>0.255162225820829</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2623123784470487</v>
+        <v>-0.2623152162271145</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2366580315613873</v>
+        <v>-0.2366577275765754</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.06677462750004423</v>
+        <v>-0.06678122718484626</v>
       </c>
       <c r="I10" t="n">
-        <v>0.186687509936757</v>
+        <v>0.1866842069862713</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02990144203954125</v>
+        <v>0.02989139572328543</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.08034886091588241</v>
+        <v>-0.08034557224561809</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1637275311944563</v>
+        <v>-0.1637350146122276</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.00917509647346418</v>
+        <v>-0.009168885050381837</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.04130584580988823</v>
+        <v>-0.04130946925861298</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1509793528940934</v>
+        <v>0.1509744314828225</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1527259905337471</v>
+        <v>-0.1527334810355685</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.08702400974381995</v>
+        <v>-0.08702911442092963</v>
       </c>
     </row>
     <row r="11">
@@ -1044,55 +1049,55 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1089188578001027</v>
+        <v>-0.1089239121346346</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.03291119029085397</v>
+        <v>-0.03290981282705194</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.004568629074206131</v>
+        <v>-0.004574775415538714</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08454527217265456</v>
+        <v>0.08452891678834798</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05629361931572446</v>
+        <v>-0.05629820108862304</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1781126722146178</v>
+        <v>-0.1781135863358454</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01397864288864214</v>
+        <v>-0.01398933307941498</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1207979239935361</v>
+        <v>0.1207929392318885</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02990144203954125</v>
+        <v>0.02989139572328543</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1269282206922364</v>
+        <v>-0.1269247801468036</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02660141681197986</v>
+        <v>0.02658113680870443</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1351219030942835</v>
+        <v>-0.1351061482347096</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2307771653907102</v>
+        <v>-0.2307940371996383</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1332238710541036</v>
+        <v>-0.1332479025140375</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.07265546534271775</v>
+        <v>-0.07267617380339651</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1676209149475167</v>
+        <v>-0.1676416401389344</v>
       </c>
     </row>
     <row r="12">
@@ -1102,55 +1107,55 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.06042980849747077</v>
+        <v>0.06045481191960975</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004279317708373074</v>
+        <v>0.004288749201532157</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1353323101048391</v>
+        <v>0.1353406515303948</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03783970617494273</v>
+        <v>0.03784703098808202</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04911980337398569</v>
+        <v>0.04912443633068477</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0206189637574075</v>
+        <v>-0.02060065919242438</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1332992889254884</v>
+        <v>-0.1332799988085527</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1470144323185691</v>
+        <v>-0.1470126622324025</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.08034886091588241</v>
+        <v>-0.08034557224561809</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1269282206922364</v>
+        <v>-0.1269247801468036</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1760897698523138</v>
+        <v>-0.1760819684905433</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.01950302276637933</v>
+        <v>-0.01950436237623197</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07396742768596458</v>
+        <v>0.07397440923576536</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.224500907581767</v>
+        <v>-0.2244951331738845</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1488997634279682</v>
+        <v>-0.1488922117781885</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.09485298646411802</v>
+        <v>-0.09484209572285808</v>
       </c>
     </row>
     <row r="13">
@@ -1160,55 +1165,55 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.07200694831406737</v>
+        <v>-0.07200721574068904</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08360196359806447</v>
+        <v>0.08360710229283419</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.08327739985458649</v>
+        <v>-0.083278936877186</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01284317346197137</v>
+        <v>-0.0128546848893997</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1539428266063144</v>
+        <v>-0.1539463953381486</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.09048251672935047</v>
+        <v>-0.09047763086059395</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1502872731241271</v>
+        <v>-0.1502918345750388</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.226061384958911</v>
+        <v>-0.2260650664380562</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1637275311944563</v>
+        <v>-0.1637350146122276</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02660141681197986</v>
+        <v>0.02658113680870443</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1760897698523138</v>
+        <v>-0.1760819684905433</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2682194222514231</v>
+        <v>-0.2682038192885902</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1640159952727195</v>
+        <v>-0.1640227209792633</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1563851445691422</v>
+        <v>0.1563739106448194</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1857900483262825</v>
+        <v>0.1857816615562367</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.01279291728303989</v>
+        <v>-0.01280163244279309</v>
       </c>
     </row>
     <row r="14">
@@ -1218,55 +1223,55 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.06223235290669801</v>
+        <v>-0.06224258984486636</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.132680053371097</v>
+        <v>-0.1326778922424604</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02366213032305863</v>
+        <v>0.02367748914598187</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1953441468644471</v>
+        <v>-0.1953285942457748</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02690703166057098</v>
+        <v>0.02690847297289807</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.02564865319920007</v>
+        <v>-0.02565347413816375</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.03704853513272143</v>
+        <v>-0.03705798757975618</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01458500950833681</v>
+        <v>-0.01458295775546621</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.00917509647346418</v>
+        <v>-0.009168885050381837</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1351219030942835</v>
+        <v>-0.1351061482347096</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.01950302276637933</v>
+        <v>-0.01950436237623197</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2682194222514231</v>
+        <v>-0.2682038192885902</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.003743021579299671</v>
+        <v>0.003750348474320619</v>
       </c>
       <c r="P14" t="n">
-        <v>0.03420877551322544</v>
+        <v>0.03422727857226083</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2072048230207576</v>
+        <v>-0.2071894468121147</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.2625041272736202</v>
+        <v>-0.2624907265587788</v>
       </c>
     </row>
     <row r="15">
@@ -1276,55 +1281,55 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1392657276480948</v>
+        <v>-0.1392607199602888</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1107287040595184</v>
+        <v>-0.1107241016210228</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2928466533276219</v>
+        <v>-0.2928443648818424</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1935932745111474</v>
+        <v>-0.1935975797300928</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.03083024928601621</v>
+        <v>-0.03083520774708307</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.07476151082895501</v>
+        <v>-0.07475468667727389</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0393037989885729</v>
+        <v>-0.03930376538405828</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04841577278798278</v>
+        <v>0.04841205060502528</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.04130584580988823</v>
+        <v>-0.04130946925861298</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2307771653907102</v>
+        <v>-0.2307940371996383</v>
       </c>
       <c r="L15" t="n">
-        <v>0.07396742768596458</v>
+        <v>0.07397440923576536</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1640159952727195</v>
+        <v>-0.1640227209792633</v>
       </c>
       <c r="N15" t="n">
-        <v>0.003743021579299671</v>
+        <v>0.003750348474320619</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1374481578308513</v>
+        <v>0.1374457465795193</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.07202347247787091</v>
+        <v>-0.07202787073353165</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.1251917306421194</v>
+        <v>-0.1252016376579099</v>
       </c>
     </row>
     <row r="16">
@@ -1334,55 +1339,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0916503972308273</v>
+        <v>-0.09165673432709796</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2412834037869715</v>
+        <v>-0.2412801869186034</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2555073431239664</v>
+        <v>-0.2555084197943746</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1935707870142529</v>
+        <v>-0.1935833410621786</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2615975856257569</v>
+        <v>-0.2616020899469228</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1284688276245625</v>
+        <v>-0.128467717265563</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0394168404907396</v>
+        <v>0.03940844743962038</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07197770583720992</v>
+        <v>0.07197671422373629</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1509793528940934</v>
+        <v>0.1509744314828225</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1332238710541036</v>
+        <v>-0.1332479025140375</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.224500907581767</v>
+        <v>-0.2244951331738845</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1563851445691422</v>
+        <v>0.1563739106448194</v>
       </c>
       <c r="N16" t="n">
-        <v>0.03420877551322544</v>
+        <v>0.03422727857226083</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1374481578308513</v>
+        <v>0.1374457465795193</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.06229849882199429</v>
+        <v>0.06228850204993441</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.03531380260550299</v>
+        <v>-0.03532311162662642</v>
       </c>
     </row>
     <row r="17">
@@ -1392,55 +1397,55 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2861192760870436</v>
+        <v>0.2861194120485466</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.3049965723763982</v>
+        <v>-0.3049929745683377</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2622539373202679</v>
+        <v>-0.2622522932892458</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.191839201031825</v>
+        <v>-0.1918499048493386</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3386445783876008</v>
+        <v>-0.3386449652654847</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1024438562367907</v>
+        <v>0.1024476202220046</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1225276578364418</v>
+        <v>0.1225239629321348</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08301605333097707</v>
+        <v>0.08301192870807282</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1527259905337471</v>
+        <v>-0.1527334810355685</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.07265546534271775</v>
+        <v>-0.07267617380339651</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1488997634279682</v>
+        <v>-0.1488922117781885</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1857900483262825</v>
+        <v>0.1857816615562367</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2072048230207576</v>
+        <v>-0.2071894468121147</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.07202347247787091</v>
+        <v>-0.07202787073353165</v>
       </c>
       <c r="P17" t="n">
-        <v>0.06229849882199429</v>
+        <v>0.06228850204993441</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1277307311077543</v>
+        <v>0.1277250932508447</v>
       </c>
     </row>
     <row r="18">
@@ -1450,52 +1455,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09085914594505834</v>
+        <v>-0.09085050779983372</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.01425591132601753</v>
+        <v>-0.0142498768740238</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1440354780577895</v>
+        <v>-0.1440326201203641</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.05437715338077125</v>
+        <v>-0.05438506220264985</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.01876771230800976</v>
+        <v>-0.01877049991952432</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1361311127764178</v>
+        <v>-0.1361213172195284</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02497911170223049</v>
+        <v>0.02498184186088281</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1417532282688239</v>
+        <v>-0.1417578894202756</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.08702400974381995</v>
+        <v>-0.08702911442092963</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1676209149475167</v>
+        <v>-0.1676416401389344</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.09485298646411802</v>
+        <v>-0.09484209572285808</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.01279291728303989</v>
+        <v>-0.01280163244279309</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2625041272736202</v>
+        <v>-0.2624907265587788</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1251917306421194</v>
+        <v>-0.1252016376579099</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.03531380260550299</v>
+        <v>-0.03532311162662642</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1277307311077543</v>
+        <v>0.1277250932508447</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
